--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487885_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487885_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3448</v>
+        <v>6.2156</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9196</v>
+        <v>4.3482</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4252</v>
+        <v>1.8674</v>
       </c>
       <c r="G2" t="n">
         <v>6.3803</v>
@@ -610,13 +610,13 @@
         <v>0.8325</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3401</v>
+        <v>1.2109</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1024</v>
+        <v>0.531</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2377</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>-1.1675</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4483</v>
+        <v>5.5301</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1246</v>
+        <v>5.089</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3237</v>
+        <v>0.4412</v>
       </c>
       <c r="G3" t="n">
         <v>5.6496</v>
@@ -688,13 +688,13 @@
         <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1795</v>
+        <v>-0.0977</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2767</v>
+        <v>0.6877</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9028</v>
+        <v>-0.7854</v>
       </c>
       <c r="V3" t="n">
         <v>-0.23</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4389</v>
+        <v>3.2348</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7826</v>
+        <v>2.4611</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6563</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.3793</v>
@@ -766,13 +766,13 @@
         <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7026</v>
+        <v>0.4986</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9316</v>
+        <v>0.6101</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2289</v>
+        <v>-0.1115</v>
       </c>
       <c r="V4" t="n">
         <v>2.565</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GARCIA-ABRIL GUERRERO</t>
+          <t>I. ORDOÑEZ OCHOA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6833</v>
+        <v>2.5077</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1779</v>
+        <v>2.9423</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4946</v>
+        <v>-0.4346</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0366</v>
+        <v>4.0453</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9191</v>
+        <v>4.3817</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1176</v>
+        <v>-0.3364</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5102</v>
+        <v>3.9068</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9314</v>
+        <v>3.9248</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5788</v>
+        <v>-0.018</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5264</v>
+        <v>0.1385</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9877</v>
+        <v>0.4569</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4613</v>
+        <v>-0.3184</v>
       </c>
       <c r="P5" t="n">
         <v>-1.6649</v>
@@ -844,28 +844,28 @@
         <v>0.4162</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0629</v>
+        <v>0.8349</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1027</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0397</v>
+        <v>0.1782</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.7513</v>
+        <v>-0.7076</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3538</v>
+        <v>0.4599</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3975</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ORDOÑEZ OCHOA</t>
+          <t>J. GARCIA-ABRIL GUERRERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4093</v>
+        <v>1.738</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0495</v>
+        <v>2.3206</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6401</v>
+        <v>-0.5827</v>
       </c>
       <c r="G6" t="n">
-        <v>4.0453</v>
+        <v>4.0366</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3817</v>
+        <v>3.9191</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3364</v>
+        <v>0.1176</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9068</v>
+        <v>3.5102</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9248</v>
+        <v>2.9314</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.018</v>
+        <v>0.5788</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1385</v>
+        <v>0.5264</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4569</v>
+        <v>0.9877</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3184</v>
+        <v>-0.4613</v>
       </c>
       <c r="P6" t="n">
         <v>-1.6649</v>
@@ -922,22 +922,22 @@
         <v>0.4162</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7366</v>
+        <v>1.1176</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7639</v>
+        <v>1.2454</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0273</v>
+        <v>-0.1278</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7076</v>
+        <v>-1.7513</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4599</v>
+        <v>-0.3538</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8426</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6215</v>
+        <v>1.1929</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7789</v>
+        <v>-0.5734</v>
       </c>
       <c r="G7" t="n">
         <v>1.7557</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6831</v>
+        <v>-0.9062</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3229</v>
+        <v>-0.1057</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.006</v>
+        <v>-0.8005</v>
       </c>
       <c r="V7" t="n">
         <v>-0.23</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2534</v>
+        <v>-0.0391</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1222</v>
+        <v>0.3365</v>
       </c>
       <c r="F8" t="n">
         <v>-0.3756</v>
@@ -1078,10 +1078,10 @@
         <v>0.2081</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6367</v>
+        <v>-0.4224</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.1491</v>
       </c>
       <c r="U8" t="n">
         <v>-0.5715</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3349</v>
+        <v>-0.5213</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1994</v>
+        <v>0.3066</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5343</v>
+        <v>-0.8279</v>
       </c>
       <c r="G9" t="n">
         <v>2.2147</v>
@@ -1156,13 +1156,13 @@
         <v>0.2081</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3196</v>
+        <v>-0.5061</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3667</v>
+        <v>-0.2595</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0471</v>
+        <v>-0.2465</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3975</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. HANNA</t>
+          <t>E. ARQUES LOPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2167</v>
+        <v>-0.5636</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3322</v>
+        <v>0.4914</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5489</v>
+        <v>-1.055</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6817</v>
+        <v>-0.585</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2557</v>
+        <v>0.3947</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5739</v>
+        <v>-0.9797</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3513</v>
+        <v>0.2359</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0355</v>
+        <v>1.4687</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6842</v>
+        <v>-1.2328</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3304</v>
+        <v>-0.8209</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2202</v>
+        <v>-1.074</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1102</v>
+        <v>0.2531</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4821</v>
+        <v>-1.1461</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0621</v>
+        <v>0.1286</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5442</v>
+        <v>-1.2747</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1675</v>
+        <v>1.1675</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. ARQUES LOPEZ</t>
+          <t>J. HANNA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3519</v>
+        <v>-1.3899</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.473</v>
+        <v>-0.3107</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8789</v>
+        <v>-1.0791</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.585</v>
+        <v>1.6817</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3947</v>
+        <v>2.2557</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9797</v>
+        <v>-0.5739</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2359</v>
+        <v>1.3513</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4687</v>
+        <v>2.0355</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2328</v>
+        <v>-0.6842</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8209</v>
+        <v>0.3304</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.074</v>
+        <v>0.2202</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2531</v>
+        <v>0.1102</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9343</v>
+        <v>-0.6553</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8358</v>
+        <v>0.4191</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0986</v>
+        <v>-1.0745</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1675</v>
+        <v>-1.1675</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.934</v>
+        <v>-2.2555</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3284</v>
+        <v>-1.6499</v>
       </c>
       <c r="F12" t="n">
         <v>-0.6056</v>
@@ -1390,10 +1390,10 @@
         <v>0.2081</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2857</v>
+        <v>-0.0357</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7144</v>
+        <v>0.3929</v>
       </c>
       <c r="U12" t="n">
         <v>-0.4286</v>
@@ -1426,10 +1426,10 @@
         <v>15.0763</v>
       </c>
       <c r="E13" t="n">
-        <v>17.5281</v>
+        <v>17.528</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4517</v>
+        <v>-2.4516</v>
       </c>
       <c r="G13" t="n">
         <v>25.6166</v>
@@ -1438,7 +1438,7 @@
         <v>23.6573</v>
       </c>
       <c r="I13" t="n">
-        <v>1.959499999999999</v>
+        <v>1.9595</v>
       </c>
       <c r="J13" t="n">
         <v>22.7615</v>
@@ -1447,7 +1447,7 @@
         <v>19.7614</v>
       </c>
       <c r="L13" t="n">
-        <v>3.0001</v>
+        <v>3.000099999999999</v>
       </c>
       <c r="M13" t="n">
         <v>2.8552</v>
@@ -1468,16 +1468,16 @@
         <v>6.243499999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1074</v>
+        <v>-0.1075000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>4.4556</v>
+        <v>4.455500000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.5628</v>
+        <v>-4.5629</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.148899999999999</v>
+        <v>-3.1489</v>
       </c>
       <c r="W13" t="n">
         <v>3.8386</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5569</v>
+        <v>1.2085</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0835</v>
+        <v>1.6549</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.4464</v>
       </c>
       <c r="G14" t="n">
         <v>-0.4528</v>
@@ -1546,13 +1546,13 @@
         <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7204</v>
+        <v>1.372</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5931</v>
+        <v>1.1645</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1273</v>
+        <v>0.2075</v>
       </c>
       <c r="V14" t="n">
         <v>-1.1675</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. TSEGAKELE</t>
+          <t>D. ÁLVAREZ FRANCO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2144</v>
+        <v>0.3215</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4147</v>
+        <v>0.289</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2003</v>
+        <v>0.0325</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.6745</v>
+        <v>-0.1662</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.8125</v>
+        <v>-0.0788</v>
       </c>
       <c r="I15" t="n">
-        <v>0.138</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1757</v>
+        <v>-0.0682</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8811</v>
+        <v>0.0192</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7054</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.4988</v>
+        <v>-0.098</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.9314</v>
+        <v>-0.098</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5674</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6402</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3604</v>
+        <v>0.3572</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7202</v>
+        <v>-0.2857</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9629</v>
+        <v>0.294</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1506</v>
+        <v>1.6148</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1876</v>
+        <v>-1.3207</v>
       </c>
       <c r="G16" t="n">
         <v>-1.8072</v>
@@ -1702,13 +1702,13 @@
         <v>1.6649</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1052</v>
+        <v>0.4363</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4344</v>
+        <v>-0.1014</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6708</v>
+        <v>0.5376</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6738</v>
+        <v>0.2355</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6405999999999999</v>
+        <v>4.7128</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0332</v>
+        <v>-4.4773</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3232</v>
+        <v>0.0209</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7631</v>
+        <v>-1.3115</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5601</v>
+        <v>1.3324</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0086</v>
+        <v>3.8831</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3026</v>
+        <v>1.6281</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3112</v>
+        <v>2.2549</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3146</v>
+        <v>-3.8622</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0657</v>
+        <v>-2.9397</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7511</v>
+        <v>-0.9225</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3289</v>
+        <v>-0.7635</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2298</v>
+        <v>-0.4648</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9009</v>
+        <v>-0.2988</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4599</v>
+        <v>0.3538</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4599</v>
+        <v>2.3351</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. ÁLVAREZ FRANCO</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1072</v>
+        <v>0.1189</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0747</v>
+        <v>-0.431</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0325</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1662</v>
+        <v>-1.3232</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0788</v>
+        <v>-0.7631</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.5601</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0682</v>
+        <v>-1.0086</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0192</v>
+        <v>0.3026</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-1.3112</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.098</v>
+        <v>-0.3146</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.098</v>
+        <v>-1.0657</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.7511</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1429</v>
+        <v>0.774</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1429</v>
+        <v>1.1583</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2857</v>
+        <v>-0.3842</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>A. TSEGAKELE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6868</v>
+        <v>-0.0803</v>
       </c>
       <c r="E19" t="n">
-        <v>4.3913</v>
+        <v>1.9145</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.0782</v>
+        <v>-1.9948</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0209</v>
+        <v>-3.6745</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3115</v>
+        <v>-3.8125</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3324</v>
+        <v>0.138</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8831</v>
+        <v>-0.1757</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6281</v>
+        <v>-0.8811</v>
       </c>
       <c r="L19" t="n">
-        <v>2.2549</v>
+        <v>0.7054</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.8622</v>
+        <v>-3.4988</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.9397</v>
+        <v>-2.9314</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9225</v>
+        <v>-0.5674</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.6649</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6858</v>
+        <v>1.3455</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7862</v>
+        <v>1.8603</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8996</v>
+        <v>-0.5147</v>
       </c>
       <c r="V19" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X19" t="n">
         <v>0.3538</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.3351</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-1.9813</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9246</v>
+        <v>-0.2904</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0557</v>
+        <v>0.8015</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8689</v>
+        <v>-1.0919</v>
       </c>
       <c r="G20" t="n">
         <v>-4.2505</v>
@@ -2014,13 +2014,13 @@
         <v>2.2893</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2579</v>
+        <v>0.3764</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5780999999999999</v>
+        <v>0.2791</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6798</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>2.3351</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. DUKE TOUSSAINT</t>
+          <t>D. RAMÍREZ SÁNCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8833</v>
+        <v>-2.6771</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3925</v>
+        <v>-0.4393</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4908</v>
+        <v>-2.2377</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7129</v>
+        <v>-3.8566</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0835</v>
+        <v>-2.8998</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.9568</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1369</v>
+        <v>-1.1785</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5401</v>
+        <v>-1.2177</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5968</v>
+        <v>0.0392</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.576</v>
+        <v>-2.6781</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5434</v>
+        <v>-1.6821</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0326</v>
+        <v>-0.996</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.443</v>
+        <v>0.5552</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3419</v>
+        <v>0.7392</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1011</v>
+        <v>-0.184</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5213</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. RAMÍREZ SÁNCHEZ</t>
+          <t>I. DUKE TOUSSAINT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.824</v>
+        <v>-2.692</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2966</v>
+        <v>-2.2853</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5274</v>
+        <v>-0.4067</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.8566</v>
+        <v>-2.7129</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.8998</v>
+        <v>-2.0835</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9568</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1785</v>
+        <v>-1.1369</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2177</v>
+        <v>-0.5401</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0392</v>
+        <v>-0.5968</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6781</v>
+        <v>-1.576</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6821</v>
+        <v>-1.5434</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.996</v>
+        <v>-0.0326</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6244</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5917</v>
+        <v>-0.2517</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1181</v>
+        <v>-0.2347</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4736</v>
+        <v>-0.0169</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.5213</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3936</v>
+        <v>-3.5158</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3533</v>
+        <v>-0.7104</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0403</v>
+        <v>-2.8055</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4569</v>
@@ -2248,13 +2248,13 @@
         <v>0.6244</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3936</v>
+        <v>-0.5158</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6929</v>
+        <v>-0.05</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7007</v>
+        <v>-0.4658</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1675</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8791</v>
+        <v>-5.1417</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2056</v>
+        <v>-4.6698</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6735</v>
+        <v>-0.4719</v>
       </c>
       <c r="G24" t="n">
         <v>-4.9367</v>
@@ -2326,13 +2326,13 @@
         <v>1.0406</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1724</v>
+        <v>-0.435</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6805</v>
+        <v>-0.1447</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4919</v>
+        <v>-0.2903</v>
       </c>
       <c r="V24" t="n">
         <v>0.23</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.0762</v>
+        <v>-12.2189</v>
       </c>
       <c r="E25" t="n">
-        <v>2.451700000000002</v>
+        <v>2.451700000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-17.528</v>
+        <v>-14.6705</v>
       </c>
       <c r="G25" t="n">
         <v>-25.6166</v>
@@ -2386,16 +2386,16 @@
         <v>1.0408</v>
       </c>
       <c r="M25" t="n">
-        <v>-22.7614</v>
+        <v>-22.76140000000001</v>
       </c>
       <c r="N25" t="n">
         <v>-19.7613</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.0001</v>
+        <v>-3.000099999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>7.284099999999999</v>
+        <v>7.2841</v>
       </c>
       <c r="Q25" t="n">
         <v>-6.243599999999999</v>
@@ -2404,19 +2404,19 @@
         <v>13.5276</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1073999999999995</v>
+        <v>2.9648</v>
       </c>
       <c r="T25" t="n">
-        <v>4.5629</v>
+        <v>4.563</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.4554</v>
+        <v>-1.5981</v>
       </c>
       <c r="V25" t="n">
         <v>3.1489</v>
       </c>
       <c r="W25" t="n">
-        <v>6.9875</v>
+        <v>6.987500000000002</v>
       </c>
       <c r="X25" t="n">
         <v>-3.8387</v>
